--- a/Assets/Project/Csv/Crops.xlsx
+++ b/Assets/Project/Csv/Crops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E415D8-C082-4CFA-B2B7-5FBC7472F300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA404D9-E679-4A7E-87E2-2456A659F60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,14 @@
   </si>
   <si>
     <t>딸기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브로콜리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -455,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC38FBB7-EF70-4387-BA44-4B6A19040DF1}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.125" bestFit="1" customWidth="1"/>
@@ -537,6 +545,28 @@
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>302</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>303</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Project/Csv/Crops.xlsx
+++ b/Assets/Project/Csv/Crops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA404D9-E679-4A7E-87E2-2456A659F60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BAEB20-EF3F-4C5B-ABA4-FC8EFE3969E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,14 +71,6 @@
   </si>
   <si>
     <t>딸기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>브로콜리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC38FBB7-EF70-4387-BA44-4B6A19040DF1}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.125" bestFit="1" customWidth="1"/>
@@ -502,6 +494,9 @@
       <c r="D2">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>1001</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -516,6 +511,9 @@
       <c r="D3">
         <v>11</v>
       </c>
+      <c r="E3">
+        <v>1101</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -530,6 +528,9 @@
       <c r="D4">
         <v>13</v>
       </c>
+      <c r="E4">
+        <v>1201</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -544,27 +545,8 @@
       <c r="D5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>302</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>303</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
+      <c r="E5">
+        <v>1301</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Project/Csv/Crops.xlsx
+++ b/Assets/Project/Csv/Crops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BAEB20-EF3F-4C5B-ABA4-FC8EFE3969E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D69EB18-4210-4C75-B9E6-41A898CCFDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
   </bookViews>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1001</v>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1101</v>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1201</v>
@@ -543,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1301</v>

--- a/Assets/Project/Csv/Crops.xlsx
+++ b/Assets/Project/Csv/Crops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D69EB18-4210-4C75-B9E6-41A898CCFDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55DF514-C37D-48C0-84BD-3CFEDD77A0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
+    <workbookView xWindow="1455" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1001</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -512,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1101</v>
+        <v>10101</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1201</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1301</v>
+        <v>10301</v>
       </c>
     </row>
   </sheetData>
